--- a/data/demo/Linkbits-Sales-2026-07-20~2026-07-20.xlsx
+++ b/data/demo/Linkbits-Sales-2026-07-20~2026-07-20.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
   <si>
     <t>2026-07-20</t>
   </si>
@@ -23,22 +23,22 @@
     <t>Audífonos Inalámbricos para la Cabeza, Recargables y Multifuncionales - Conectan a Varios Dispositivos, soportan Radio FM, Tarjeta TF y AUX - 4 Horas de Reproducción Musical - Ideal para Trabajo Cotidiano, Juegos y Estudio</t>
   </si>
   <si>
-    <t>MX$2,990.00</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>1.48</t>
-  </si>
-  <si>
-    <t>MX$59.80</t>
+    <t>MX$4,758.00</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>1.33</t>
+  </si>
+  <si>
+    <t>MX$54.06</t>
   </si>
   <si>
     <t>602978090117530</t>
@@ -68,144 +68,177 @@
     <t>Soporte Articulado de Pared para TV LCD LED Smart de 14 a 55 Pulgadas, Brazo Telescópico 3 Brazos Extensible y Retráctil, Giro Horizontal ±90°, Inclinación ±15°, Carga Hasta 25kg, Compatible VESA 75x75 hasta 400x400, Para Pared de Ladrillo, Madera y Hormigón</t>
   </si>
   <si>
-    <t>MX$936.00</t>
+    <t>MX$1,017.00</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>1.86</t>
+  </si>
+  <si>
+    <t>MX$145.28</t>
+  </si>
+  <si>
+    <t>608113864355784</t>
+  </si>
+  <si>
+    <t>Audífonos diadema over-ear Bluetooth 5.4 con micrófono HD y baja latencia, plegables ergonómicos para estudiar, ver series y jugar en celular, laptop y consola, conexión estable sin cortes</t>
+  </si>
+  <si>
+    <t>MX$831.00</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>1.36</t>
+  </si>
+  <si>
+    <t>MX$75.54</t>
+  </si>
+  <si>
+    <t>604835730556993</t>
+  </si>
+  <si>
+    <t>Bocina portátil Inalámbrico, de 3 pulgadas, tamaño de bolsillo, 170 g, con asa, compatible con TF, USB y Micro SD, con radio FM y función TWS (True Wireless Stereo), adecuada para relajarse en casa o viajar al aire libre.</t>
+  </si>
+  <si>
+    <t>MX$765.00</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>2.57</t>
+  </si>
+  <si>
+    <t>MX$109.28</t>
+  </si>
+  <si>
+    <t>604920287716838</t>
+  </si>
+  <si>
+    <t>El foco de techo LED de la marca MEGALUZ con una potencia de 18 vatios tiene una iluminación fría blanca de 6500K que se puede ajustar y es de tipo incrustado. El cuerpo del foco es ultra delgado y el tamaño del orificio de perforación se puede ajustar. Está fabricado con aluminio de alta calidad, lo que lo hace resistente a la corrosión y al óxido. Tiene un voltaje de trabajo entre 85 y 265 voltios y una frecuencia de 60 hercios. Es muy adecuado para salones, habitaciones, escaleras y pasillos.</t>
+  </si>
+  <si>
+    <t>MX$565.00</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>MX$188.33</t>
+  </si>
+  <si>
+    <t>602298411512334</t>
+  </si>
+  <si>
+    <t>Musicord Altavoz Inalámbrico BT Portátil: ¡Sonido impactante, luces LED multicolores y 4 horas de autonomía! Compatible con TWS, FM, TF y USB – Imprescindible para fiestas y viajes</t>
+  </si>
+  <si>
+    <t>MX$475.00</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>MX$59.37</t>
+  </si>
+  <si>
+    <t>604583719972405</t>
+  </si>
+  <si>
+    <t>Auriculares supraaurales envolventes inalámbricos Bluetooth 5.3, con diadema metálica, orejeras de piel de proteína, ligeros y plegables, para gaming, deportes y uso diario</t>
+  </si>
+  <si>
+    <t>MX$325.00</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>MX$65.00</t>
+  </si>
+  <si>
+    <t>602329550025647</t>
+  </si>
+  <si>
+    <t>MEGALUZ Foco Emergencia Recargable 36W Alta Luminosidad 2500 Lúmenes, Bombilla Portátil Luz de Emergencia con Gancho Colgante, 3 Modos de Luz (Intensa/Normal/Intermitente), Batería Recargable Carga Micro USB, Lampara para Camping, Tianguis, Apagones Casa, Luz para Jardín Nocturno</t>
+  </si>
+  <si>
+    <t>MX$300.03</t>
+  </si>
+  <si>
+    <t>MX$75.00</t>
+  </si>
+  <si>
+    <t>604756323999048</t>
+  </si>
+  <si>
+    <t>link bits Barra de Sonido para TV, 2x2" Altavoces + 2 Membranas de Graves, Sonido Claro ≥80dB, Bluetooth Inalámbrico, Conexiones AUX/USB, Diseño Compacto 76cm, Sonido Envolvente 3D para Cine en Casa, PC, Juegos y Fiestas</t>
+  </si>
+  <si>
+    <t>MX$260.00</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>605063145692961</t>
+  </si>
+  <si>
+    <t>Subwoofer Portátil Inalámbrico con Luces RGB, Sonido de Alta Potencia y Batería Duradera, TWS TF USB, Perfecto para Campamento Fiestas y Entretenimiento en Casa, Regalo Ideal para Amigos, Familia y Celebraciones Festivas</t>
+  </si>
+  <si>
+    <t>MX$234.00</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>2.00</t>
-  </si>
-  <si>
-    <t>MX$156.00</t>
-  </si>
-  <si>
-    <t>608113864355784</t>
-  </si>
-  <si>
-    <t>Audífonos diadema over-ear Bluetooth 5.4 con micrófono HD y baja latencia, plegables ergonómicos para estudiar, ver series y jugar en celular, laptop y consola, conexión estable sin cortes</t>
-  </si>
-  <si>
-    <t>MX$604.00</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>1.57</t>
-  </si>
-  <si>
-    <t>MX$86.28</t>
-  </si>
-  <si>
-    <t>602329550025647</t>
-  </si>
-  <si>
-    <t>MEGALUZ - Lámpara de emergencia portátil móvil de 36 vatios, con un gancho incorporado. Tiene luz blanca de 6500K, y se puede ajustar en múltiples modos de iluminación. Es una lámpara colgante con un puerto USB y una lámpara de carga USB. Es adecuada como lámpara de emergencia LED para el hogar, lámpara de emergencia de bombilla para acampar al aire libre, o para iluminar jardines en mercados nocturnos. Te brinda una experiencia de iluminación súper brillante.</t>
-  </si>
-  <si>
-    <t>MX$300.03</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>MX$75.00</t>
-  </si>
-  <si>
-    <t>602298411512334</t>
-  </si>
-  <si>
-    <t>Musicord Altavoz Inalámbrico BT Portátil: ¡Sonido impactante, luces LED multicolores y 4 horas de autonomía! Compatible con TWS, FM, TF y USB – Imprescindible para fiestas y viajes</t>
-  </si>
-  <si>
-    <t>MX$268.00</t>
-  </si>
-  <si>
-    <t>MX$53.60</t>
-  </si>
-  <si>
-    <t>604920287716838</t>
-  </si>
-  <si>
-    <t>El foco de techo LED de la marca MEGALUZ con una potencia de 18 vatios tiene una iluminación fría blanca de 6500K que se puede ajustar y es de tipo incrustado. El cuerpo del foco es ultra delgado y el tamaño del orificio de perforación se puede ajustar. Está fabricado con aluminio de alta calidad, lo que lo hace resistente a la corrosión y al óxido. Tiene un voltaje de trabajo entre 85 y 265 voltios y una frecuencia de 60 hercios. Es muy adecuado para salones, habitaciones, escaleras y pasillos.</t>
-  </si>
-  <si>
-    <t>MX$265.00</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>604756323999048</t>
-  </si>
-  <si>
-    <t>link bits Barra de Sonido para TV, 2x2" Altavoces + 2 Membranas de Graves, Sonido Claro ≥80dB, Bluetooth Inalámbrico, Conexiones AUX/USB, Diseño Compacto 76cm, Sonido Envolvente 3D para Cine en Casa, PC, Juegos y Fiestas</t>
-  </si>
-  <si>
-    <t>MX$260.00</t>
-  </si>
-  <si>
-    <t>604583719972405</t>
-  </si>
-  <si>
-    <t>Auriculares supraaurales envolventes inalámbricos Bluetooth 5.3, con diadema metálica, orejeras de piel de proteína, ligeros y plegables, para gaming, deportes y uso diario</t>
-  </si>
-  <si>
-    <t>MX$195.00</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>MX$65.00</t>
-  </si>
-  <si>
-    <t>605063145692961</t>
-  </si>
-  <si>
-    <t>Subwoofer Portátil Inalámbrico con Luces RGB, Sonido de Alta Potencia y Batería Duradera, TWS TF USB, Perfecto para Campamento Fiestas y Entretenimiento en Casa</t>
-  </si>
-  <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>MX$48.75</t>
-  </si>
-  <si>
-    <t>604835730556993</t>
-  </si>
-  <si>
-    <t>Bocina portátil Inalámbrico, de 3 pulgadas, tamaño de bolsillo, 170 g, con asa, compatible con TF, USB y Micro SD, con radio FM y función TWS (True Wireless Stereo), adecuada para relajarse en casa o viajar al aire libre.</t>
-  </si>
-  <si>
-    <t>MX$127.50</t>
+    <t>1.20</t>
+  </si>
+  <si>
+    <t>MX$46.80</t>
+  </si>
+  <si>
+    <t>604520050455943</t>
+  </si>
+  <si>
+    <t>La bocina portátil inalámbrica Linkbits cuenta con parlantes estéreo de dos altavoces de 3 pulgadas, luces de ambiente integradas y una batería recargable de gran capacidad que ofrece 3-4 horas de reproducción. Compatible con tarjeta TF, USB, radio FM y conexión inalámbrica, es ideal para cine en casa, fiestas al aire libre y campamentos.</t>
+  </si>
+  <si>
+    <t>MX$79.90</t>
+  </si>
+  <si>
+    <t>602285526606889</t>
+  </si>
+  <si>
+    <t>Foco de bombilla LED de la marca TIANLAI. Tensión de trabajo: 127 voltios / Potencia: 48 vatios. Luz de color blanco frío de 6500K. El cuerpo de la bombilla está herméticamente sellado de forma integral, que es resistente al polvo y a los insectos, prolongando su vida útil. Tiene un conector enroscado estándar E27, lo que hace que la instalación sea muy fácil. Es muy adecuado para salones, dormitorios, estudios y garajes.</t>
+  </si>
+  <si>
+    <t>MX$78.00</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>MX$42.50</t>
-  </si>
-  <si>
-    <t>602285526606889</t>
-  </si>
-  <si>
-    <t>Foco de bombilla LED de la marca TIANLAI. Tensión de trabajo: 127 voltios / Potencia: 48 vatios. Luz de color blanco frío de 6500K. El cuerpo de la bombilla está herméticamente sellado de forma integral, que es resistente al polvo y a los insectos, prolongando su vida útil. Tiene un conector enroscado estándar E27, lo que hace que la instalación sea muy fácil. Es muy adecuado para salones, dormitorios, estudios y garajes.</t>
-  </si>
-  <si>
-    <t>MX$78.00</t>
-  </si>
-  <si>
     <t>MX$39.00</t>
   </si>
   <si>
@@ -216,6 +249,21 @@
   </si>
   <si>
     <t>MX$70.00</t>
+  </si>
+  <si>
+    <t>604428782393798</t>
+  </si>
+  <si>
+    <t>Bocina Portátil , Parlante Portátil BT, Incorpora Luces De Ambiente. Posee La Función De Radio FM, La Función TWS (True Wireless Stereo), Soporta Tarjetas TF Y Se Puede Cargar A Través De USB. Tiene Forma De Cilindro, Pesa 198 Gramos Y Viene Con Un Cordón De Gancho, Lo Que La Hace Compacta Y Portátil. Ya Sea Para Relajarse En Casa, Celebrar Fiestas O Viajar, Es Una Opción Ideal.</t>
+  </si>
+  <si>
+    <t>MX$42.00</t>
+  </si>
+  <si>
+    <t>605335339264451</t>
+  </si>
+  <si>
+    <t>LINK BITS Bocina Portátil Inalámbrica 3 Pulgadas, Altavoz Bluetooth con Función TWS, Radio FM, Reproducción USB TF, Luces Ambientales, Batería Recargable 500mAh 5W, Mini Bocina Cuadrada Negra para Hogar Viaje Regalo</t>
   </si>
 </sst>
 </file>
@@ -295,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -417,19 +465,19 @@
         <v>18</v>
       </c>
       <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -437,19 +485,19 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
@@ -478,16 +526,16 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -495,28 +543,28 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -524,28 +572,28 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -553,28 +601,28 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -582,28 +630,28 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -611,28 +659,28 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -640,28 +688,28 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -669,28 +717,28 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -698,28 +746,115 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>67</v>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" t="s">
+        <v>41</v>
+      </c>
+      <c r="I17" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
